--- a/integradores/int-intermedio.xlsx
+++ b/integradores/int-intermedio.xlsx
@@ -511,14 +511,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. Comisiones: D2:D21 (meta F1, tasa F2) y F4 (cuántos alcanzaron la meta).</t>
+          <t>4. Lista desplegable en la columna Estado (I2:I41) con Pendiente y Entregado.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. Protege la hoja Comisiones dejando editables solo F1 y F2.</t>
+          <t>5. Comisiones: D2:D21 (meta F1, tasa F2) y F4 (cuántos alcanzaron la meta).</t>
         </is>
       </c>
     </row>

--- a/integradores/int-intermedio.xlsx
+++ b/integradores/int-intermedio.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pedidos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comisiones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Requisiciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -33,7 +31,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="005B3A29"/>
+      <color rgb="000F5E57"/>
       <sz val="16"/>
     </font>
     <font>
@@ -41,7 +39,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="007A4D0E"/>
+      <color rgb="000F5E57"/>
     </font>
   </fonts>
   <fills count="3">
@@ -53,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBDF"/>
+        <fgColor rgb="00DFF0EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,9 +84,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reto integrador intermedio · Base de pedidos confiable</t>
+          <t>Reto integrador · Análisis de datos · Base de requisiciones confiable</t>
         </is>
       </c>
     </row>
@@ -473,7 +468,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Limpia la base de pedidos y calcula las comisiones del mes.</t>
+          <t>Depura la base de requisiciones, conviértela en tabla con totales y resume por área.</t>
         </is>
       </c>
     </row>
@@ -490,35 +485,35 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. Pedidos: quita los duplicados.</t>
+          <t>1. Requisiciones: quita los duplicados.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2. Convierte los pedidos en la tabla «Pedidos» con la columna calculada Importe y la fila de totales.</t>
+          <t>2. Convierte los datos en la tabla «Requisiciones» con la columna calculada Importe y la fila de totales.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3. Formato condicional para los pedidos con Estado «Pendiente».</t>
+          <t>3. Formato condicional para las requisiciones con Estado «Pendiente».</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. Lista desplegable en la columna Estado (I2:I41) con Pendiente y Entregado.</t>
+          <t>4. Lista desplegable en la columna Estado (I2:I41) con Surtida y Pendiente.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. Comisiones: D2:D21 (meta F1, tasa F2) y F4 (cuántos alcanzaron la meta).</t>
+          <t>5. Hoja nueva con una tabla dinámica: suma de Importe por Área.</t>
         </is>
       </c>
     </row>
@@ -528,7 +523,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Importante: no cambies los nombres de las hojas ni muevas los datos de lugar. Al terminar, guarda el libro y súbelo en la página del módulo (etapa 4).</t>
+          <t>Importante: no cambies los nombres de las hojas ni muevas los datos de lugar. Al terminar, guarda el libro y súbelo en la página del módulo (etapa 4). Datos ficticios con fines didácticos.</t>
         </is>
       </c>
     </row>
@@ -548,12 +543,12 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -570,17 +565,17 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Área</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>Sede</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
@@ -595,7 +590,7 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Compromiso</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
@@ -606,162 +601,162 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2501</v>
+        <v>3001</v>
       </c>
       <c r="B2" s="6" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2502</v>
+        <v>3002</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>45932</v>
+        <v>45934</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clínica Dental Sonrisa</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chai latte</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>54</v>
+        <v>290</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>45939</v>
+        <v>45936</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2503</v>
+        <v>3003</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45932</v>
+        <v>45935</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Frappé moka</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>45934</v>
+        <v>45942</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2504</v>
+        <v>3004</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45934</v>
+        <v>45938</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Panini caprese</t>
+          <t>Solución salina 0.9 % 500 mL (caja 24)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>85</v>
+        <v>520</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2505</v>
+        <v>3005</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>45934</v>
+        <v>45939</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -771,34 +766,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Americano</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2505</v>
+        <v>3005</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>45934</v>
+        <v>45939</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -808,71 +803,71 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Americano</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2506</v>
+        <v>3006</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Té verde</t>
+          <t>Equipo de venoclisis (caja 25)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>38</v>
+        <v>380</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2507</v>
+        <v>3007</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45936</v>
+        <v>45941</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hospital San Rafael</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -882,108 +877,108 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sándwich de pavo</t>
+          <t>Guantes de nitrilo (caja 100)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>45938</v>
+        <v>45948</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2508</v>
+        <v>3008</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45936</v>
+        <v>45943</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muffin de mora</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2509</v>
+        <v>3009</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45936</v>
+        <v>45945</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Moka</t>
+          <t>Cubrebocas tricapa (caja 50)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>45939</v>
+        <v>45952</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2510</v>
+        <v>3010</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Clínica Dental Sonrisa</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -993,165 +988,165 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Café de olla</t>
+          <t>Catéter IV 22G (caja 50)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>38</v>
+        <v>640</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2511</v>
+        <v>3011</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45937</v>
+        <v>45948</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Clínica Dental Sonrisa</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Latte</t>
+          <t>Torundas de algodón (bolsa 500)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>45940</v>
+        <v>45955</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2512</v>
+        <v>3012</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45940</v>
+        <v>45949</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cold brew</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>45944</v>
+        <v>45956</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2512</v>
+        <v>3012</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45940</v>
+        <v>45949</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cold brew</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>45944</v>
+        <v>45956</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2513</v>
+        <v>3013</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Latte helado</t>
+          <t>Alcohol etílico 70 % (1 L)</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>58</v>
-      </c>
       <c r="H16" s="6" t="n">
-        <v>45942</v>
+        <v>45954</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1161,88 +1156,88 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2514</v>
+        <v>3014</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>45942</v>
+        <v>45951</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colegio Montebello</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sándwich de pavo</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>78</v>
+        <v>290</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>45949</v>
+        <v>45959</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2515</v>
+        <v>3015</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>45943</v>
+        <v>45952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hospital San Rafael</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bagel con queso crema</t>
+          <t>Solución salina 0.9 % 500 mL (caja 24)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>45</v>
+        <v>520</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>45946</v>
+        <v>45957</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2516</v>
+        <v>3016</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>45944</v>
+        <v>45953</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Agencia Pixel</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1252,34 +1247,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2517</v>
+        <v>3017</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1289,71 +1284,71 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Catéter IV 22G (caja 50)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>40</v>
+        <v>640</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>45952</v>
+        <v>45962</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2518</v>
+        <v>3018</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45945</v>
+        <v>45955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inmobiliaria Cumbres</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pay de queso</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>45951</v>
+        <v>45958</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2519</v>
+        <v>3019</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45947</v>
+        <v>45956</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Agencia Pixel</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1363,145 +1358,145 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2520</v>
+        <v>3020</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45947</v>
+        <v>45956</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Té verde</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>45953</v>
+        <v>45962</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2520</v>
+        <v>3020</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45947</v>
+        <v>45956</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Té verde</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>45953</v>
+        <v>45962</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2521</v>
+        <v>3021</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45947</v>
+        <v>45956</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gimnasio Fénix</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sándwich de pavo</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>78</v>
+        <v>290</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2522</v>
+        <v>3022</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>45949</v>
+        <v>45957</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1511,71 +1506,71 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Galleta de avena</t>
+          <t>Jeringas 5 mL (caja 100)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2523</v>
+        <v>3023</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inmobiliaria Cumbres</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Solución salina 0.9 % 500 mL (caja 24)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>52</v>
+        <v>520</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>45953</v>
+        <v>45963</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2524</v>
+        <v>3024</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1585,34 +1580,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sándwich de pavo</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>78</v>
+        <v>290</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>45956</v>
+        <v>45962</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2525</v>
+        <v>3025</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1622,34 +1617,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latte helado</t>
+          <t>Cubrebocas tricapa (caja 50)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>45960</v>
+        <v>45962</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2526</v>
+        <v>3026</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1659,182 +1654,182 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pay de queso</t>
+          <t>Torundas de algodón (bolsa 500)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>45955</v>
+        <v>45966</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2527</v>
+        <v>3027</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>45955</v>
+        <v>45960</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gimnasio Fénix</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chai latte</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>45959</v>
+        <v>45968</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2527</v>
+        <v>3027</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>45955</v>
+        <v>45960</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gimnasio Fénix</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chai latte</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>45959</v>
+        <v>45968</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2528</v>
+        <v>3028</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Galleta de avena</t>
+          <t>Tiras reactivas de glucosa (caja 50)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2529</v>
+        <v>3029</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>45957</v>
+        <v>45963</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Torundas de algodón (bolsa 500)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>45963</v>
+        <v>45970</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2530</v>
+        <v>3030</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>45958</v>
+        <v>45963</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Despacho Luna &amp; Asoc.</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1844,108 +1839,108 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chai latte</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2531</v>
+        <v>3031</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>45962</v>
+        <v>45965</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Universidad del Norte</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galleta de avena</t>
+          <t>Gasas estériles (paquete 100)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>45967</v>
+        <v>45969</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Surtida</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2532</v>
+        <v>3032</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>45963</v>
+        <v>45967</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hospital San Rafael</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frappé moka</t>
+          <t>Equipo de venoclisis (caja 25)</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2533</v>
+        <v>3033</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>45964</v>
+        <v>45967</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Consulta externa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1955,17 +1950,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Latte helado</t>
+          <t>Solución salina 0.9 % 500 mL (caja 24)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>45967</v>
+        <v>45969</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1975,125 +1970,125 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2534</v>
+        <v>3034</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>45966</v>
+        <v>45969</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hospital San Rafael</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>45971</v>
+        <v>45976</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2534</v>
+        <v>3034</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>45966</v>
+        <v>45969</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hospital San Rafael</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Espresso</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>45971</v>
+        <v>45976</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2535</v>
+        <v>3035</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Notaría 14</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chai latte</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>54</v>
+        <v>290</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>45972</v>
+        <v>45976</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Entregado</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2536</v>
+        <v>3036</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>45970</v>
+        <v>45969</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Universidad del Norte</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2103,17 +2098,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Latte helado</t>
+          <t>Torundas de algodón (bolsa 500)</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>45976</v>
+        <v>45974</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2123,34 +2118,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2537</v>
+        <v>3037</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>45970</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gimnasio Fénix</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Jeringas 5 mL (caja 100)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>45976</v>
+        <v>45978</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2160,14 +2155,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2538</v>
+        <v>3038</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>45970</v>
+        <v>45973</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gimnasio Fénix</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2177,17 +2172,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Café de olla</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>45976</v>
+        <v>45975</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2197,34 +2192,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2539</v>
+        <v>3039</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Coworking Nodo</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Latte</t>
+          <t>Tubos tapa morada (caja 100)</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2234,14 +2229,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2540</v>
+        <v>3040</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inmobiliaria Cumbres</t>
+          <t>Hospitalización</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2251,405 +2246,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Café de olla</t>
+          <t>Venda elástica 10 cm (paquete 12)</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>45976</v>
+        <v>45980</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Vendedor</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Ventas del mes</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Comisión</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>Meta mensual</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Andrea Solís</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>13187</v>
-      </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Tasa de comisión</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bruno Castillo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>10046</v>
-      </c>
-      <c r="D3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Carla Núñez</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>10897</v>
-      </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Alcanzaron la meta</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Daniel Pineda</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>6786</v>
-      </c>
-      <c r="D5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Elena Robles</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>14067</v>
-      </c>
-      <c r="D6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fernando Ibarra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>9433</v>
-      </c>
-      <c r="D7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gabriela Luna</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>10522</v>
-      </c>
-      <c r="D8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Héctor Vargas</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>12383</v>
-      </c>
-      <c r="D9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Isabel Cruz</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>15746</v>
-      </c>
-      <c r="D10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jorge Medina</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>10068</v>
-      </c>
-      <c r="D11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Karen Salazar</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>6269</v>
-      </c>
-      <c r="D12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Leonardo Ríos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>10475</v>
-      </c>
-      <c r="D13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mariana Paredes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>7688</v>
-      </c>
-      <c r="D14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Nicolás Herrera</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>11573</v>
-      </c>
-      <c r="D15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Olivia Campos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>12959</v>
-      </c>
-      <c r="D16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pablo Aguilar</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>7271</v>
-      </c>
-      <c r="D17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regina Fuentes</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>10709</v>
-      </c>
-      <c r="D18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sergio Mendoza</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>9476</v>
-      </c>
-      <c r="D19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tania Guzmán</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>5609</v>
-      </c>
-      <c r="D20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Valeria Ochoa</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>13426</v>
-      </c>
-      <c r="D21" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
